--- a/data/k-props/2026-08-01.xlsx
+++ b/data/k-props/2026-08-01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="102">
   <si>
     <t>date</t>
   </si>
@@ -145,175 +145,175 @@
     <t>2026-08-01</t>
   </si>
   <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Logan Gilbert</t>
+  </si>
+  <si>
+    <t>Jordan Hicks</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Drew Rasmussen</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Tyler Phillips</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ New York Mets</t>
+  </si>
+  <si>
+    <t>Zac Thornton</t>
+  </si>
+  <si>
     <t>Braxton Ashcraft</t>
   </si>
   <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Pittsburgh Pirates @ Cincinnati Reds</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>posted</t>
-  </si>
-  <si>
     <t>Andrew Abbott</t>
   </si>
   <si>
     <t>Opener</t>
   </si>
   <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>Jacob deGrom</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Ronel Blanco</t>
+  </si>
+  <si>
+    <t>Kohl Drake</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Parker Messick</t>
+  </si>
+  <si>
+    <t>Miles Mikolas</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Max Fried</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>David Peterson</t>
+  </si>
+  <si>
+    <t>Luinder Avila</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Walker Buehler</t>
+  </si>
+  <si>
+    <t>Payton Tolle</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Yoshinobu Yamamoto</t>
+  </si>
+  <si>
+    <t>Robert Gasser</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Brent Suter</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Athletics</t>
+  </si>
+  <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
     <t>Cristopher Sanchez</t>
   </si>
   <si>
-    <t>Philadelphia Phillies @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>Ronel Blanco</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Jacob deGrom</t>
-  </si>
-  <si>
-    <t>Parker Messick</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Kohl Drake</t>
-  </si>
-  <si>
     <t>Reynaldo Lopez</t>
   </si>
   <si>
-    <t>Washington Nationals @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Miles Mikolas</t>
-  </si>
-  <si>
-    <t>David Peterson</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Max Fried</t>
-  </si>
-  <si>
-    <t>Luinder Avila</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Walker Buehler</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>Payton Tolle</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Yoshinobu Yamamoto</t>
-  </si>
-  <si>
-    <t>Robert Gasser</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Athletics</t>
-  </si>
-  <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Logan Gilbert</t>
-  </si>
-  <si>
-    <t>Jordan Hicks</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Drew Rasmussen</t>
-  </si>
-  <si>
-    <t>Tyler Phillips</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ New York Mets</t>
-  </si>
-  <si>
-    <t>Zac Thornton</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
     <t>Reynaldo López</t>
-  </si>
-  <si>
-    <t>Brent Suter</t>
-  </si>
-  <si>
-    <t>projected_regulars</t>
   </si>
   <si>
     <t>Zach Thornton</t>
@@ -697,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ33"/>
+  <dimension ref="A1:AQ34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="43" width="16" customWidth="1"/>
@@ -841,68 +841,89 @@
       <c r="B2" t="s">
         <v>44</v>
       </c>
-      <c r="C2">
-        <v>6.5</v>
-      </c>
-      <c r="D2">
-        <v>-108</v>
-      </c>
-      <c r="E2">
-        <v>-112</v>
-      </c>
       <c r="F2">
-        <v>7.39</v>
-      </c>
-      <c r="G2">
+        <v>4.84</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2">
+        <v>4.68</v>
+      </c>
+      <c r="L2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2">
+        <v>822781</v>
+      </c>
+      <c r="O2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2">
+        <v>5.6</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0.2314</v>
+      </c>
+      <c r="U2">
+        <v>0.2159</v>
+      </c>
+      <c r="V2">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2">
-        <v>0.89</v>
-      </c>
-      <c r="J2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2">
-        <v>7.99</v>
-      </c>
-      <c r="L2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N2">
-        <v>824485</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="W2">
+        <v>121</v>
+      </c>
+      <c r="X2">
+        <v>0.1901</v>
+      </c>
+      <c r="Y2">
+        <v>0.377</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>4.21</v>
+      </c>
+      <c r="AB2">
+        <v>1.0083</v>
+      </c>
+      <c r="AC2" t="s">
         <v>49</v>
       </c>
-      <c r="P2">
-        <v>5.8</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>6</v>
-      </c>
-      <c r="AA2">
-        <v>4.14</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>47</v>
+      <c r="AD2">
+        <v>0.2172</v>
+      </c>
+      <c r="AE2">
+        <v>0.2097</v>
+      </c>
+      <c r="AF2">
+        <v>9</v>
+      </c>
+      <c r="AG2">
+        <v>0.2126</v>
+      </c>
+      <c r="AH2">
+        <v>0.2154</v>
       </c>
       <c r="AI2">
-        <v>1.0802</v>
+        <v>0.9119</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -913,17 +934,8 @@
       <c r="AL2" t="s">
         <v>50</v>
       </c>
-      <c r="AN2">
-        <v>-2.99</v>
-      </c>
-      <c r="AO2">
-        <v>2.99</v>
-      </c>
-      <c r="AP2">
-        <v>-2.39</v>
-      </c>
-      <c r="AQ2">
-        <v>2.39</v>
+      <c r="AM2">
+        <v>0.16</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
@@ -933,68 +945,89 @@
       <c r="B3" t="s">
         <v>51</v>
       </c>
-      <c r="C3">
-        <v>5.5</v>
-      </c>
-      <c r="D3">
-        <v>129</v>
-      </c>
-      <c r="E3">
-        <v>-136</v>
-      </c>
       <c r="F3">
-        <v>5.12</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>7.41</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
       </c>
-      <c r="I3">
-        <v>-0.38</v>
-      </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K3">
-        <v>5.72</v>
+        <v>7.41</v>
       </c>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3">
+        <v>823109</v>
+      </c>
+      <c r="O3" t="s">
         <v>48</v>
       </c>
-      <c r="N3">
-        <v>824485</v>
-      </c>
-      <c r="O3" t="s">
-        <v>52</v>
-      </c>
       <c r="P3">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="Q3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0.2472</v>
+      </c>
+      <c r="U3">
+        <v>0.2668</v>
+      </c>
+      <c r="V3">
+        <v>5</v>
+      </c>
+      <c r="W3">
+        <v>109</v>
+      </c>
+      <c r="X3">
+        <v>0.3028</v>
+      </c>
+      <c r="Y3">
+        <v>0.353</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.32</v>
+        <v>4.31</v>
+      </c>
+      <c r="AB3">
+        <v>1.2027</v>
       </c>
       <c r="AC3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD3">
+        <v>0.2591</v>
+      </c>
+      <c r="AE3">
+        <v>0.2311</v>
+      </c>
+      <c r="AF3">
+        <v>9</v>
+      </c>
+      <c r="AG3">
+        <v>0.2371</v>
+      </c>
+      <c r="AH3">
+        <v>0.2154</v>
       </c>
       <c r="AI3">
-        <v>1.0539</v>
+        <v>1.0378</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
@@ -1005,17 +1038,8 @@
       <c r="AL3" t="s">
         <v>50</v>
       </c>
-      <c r="AN3">
-        <v>-4.72</v>
-      </c>
-      <c r="AO3">
-        <v>4.72</v>
-      </c>
-      <c r="AP3">
-        <v>-4.12</v>
-      </c>
-      <c r="AQ3">
-        <v>4.12</v>
+      <c r="AM3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
@@ -1023,49 +1047,103 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4">
+        <v>5.51</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4">
+        <v>5.35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" t="s">
         <v>53</v>
       </c>
-      <c r="C4">
-        <v>7.5</v>
-      </c>
-      <c r="D4">
-        <v>124</v>
-      </c>
-      <c r="E4">
-        <v>-156</v>
-      </c>
-      <c r="H4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" t="s">
-        <v>47</v>
+      <c r="N4">
+        <v>823109</v>
       </c>
       <c r="O4" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="P4">
+        <v>6.1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0.2641</v>
+      </c>
+      <c r="U4">
+        <v>0.254</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4">
+        <v>130</v>
+      </c>
+      <c r="X4">
+        <v>0.2385</v>
+      </c>
+      <c r="Y4">
+        <v>0.394</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>3.94</v>
+      </c>
+      <c r="AB4">
+        <v>0.9293</v>
       </c>
       <c r="AC4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD4">
+        <v>0.2002</v>
+      </c>
+      <c r="AE4">
+        <v>0.2009</v>
+      </c>
+      <c r="AF4">
+        <v>9</v>
+      </c>
+      <c r="AG4">
+        <v>0.2106</v>
+      </c>
+      <c r="AH4">
+        <v>0.2154</v>
+      </c>
+      <c r="AI4">
+        <v>0.9487</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="AM4">
+        <v>0.16</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
@@ -1075,68 +1153,89 @@
       <c r="B5" t="s">
         <v>55</v>
       </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-      <c r="D5">
-        <v>110</v>
-      </c>
-      <c r="E5">
-        <v>-131</v>
-      </c>
       <c r="F5">
-        <v>4.88</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
+        <v>1.15</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
       </c>
-      <c r="I5">
-        <v>-0.62</v>
-      </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K5">
-        <v>5.48</v>
+        <v>0.99</v>
       </c>
       <c r="L5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5">
-        <v>824808</v>
+        <v>822944</v>
       </c>
       <c r="O5" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0.2632</v>
+      </c>
+      <c r="U5">
+        <v>0.2642</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>0.3333</v>
+      </c>
+      <c r="Y5">
+        <v>0.015</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>4.47</v>
+      </c>
+      <c r="AB5">
+        <v>0.9514</v>
+      </c>
+      <c r="AC5" t="s">
         <v>49</v>
       </c>
-      <c r="P5">
-        <v>5.8</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>6</v>
-      </c>
-      <c r="AA5">
-        <v>4.31</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>47</v>
+      <c r="AD5">
+        <v>0.205</v>
+      </c>
+      <c r="AE5">
+        <v>0.2</v>
+      </c>
+      <c r="AF5">
+        <v>9</v>
+      </c>
+      <c r="AG5">
+        <v>0.1929</v>
+      </c>
+      <c r="AH5">
+        <v>0.2154</v>
       </c>
       <c r="AI5">
-        <v>0.9994</v>
+        <v>0.88</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
@@ -1147,17 +1246,8 @@
       <c r="AL5" t="s">
         <v>50</v>
       </c>
-      <c r="AN5">
-        <v>-1.48</v>
-      </c>
-      <c r="AO5">
-        <v>1.48</v>
-      </c>
-      <c r="AP5">
-        <v>-0.88</v>
-      </c>
-      <c r="AQ5">
-        <v>0.88</v>
+      <c r="AM5">
+        <v>0.16</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
@@ -1165,52 +1255,103 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6">
+        <v>6.03</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>6.03</v>
+      </c>
+      <c r="L6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" t="s">
         <v>56</v>
       </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-      <c r="D6">
-        <v>123</v>
-      </c>
-      <c r="E6">
-        <v>-143</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" t="s">
-        <v>57</v>
-      </c>
-      <c r="N6" t="s">
-        <v>47</v>
+      <c r="N6">
+        <v>822944</v>
       </c>
       <c r="O6" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="P6">
+        <v>5.7</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0.268</v>
+      </c>
+      <c r="U6">
+        <v>0.2854</v>
+      </c>
+      <c r="V6">
+        <v>5</v>
+      </c>
+      <c r="W6">
+        <v>107</v>
+      </c>
+      <c r="X6">
+        <v>0.3178</v>
+      </c>
+      <c r="Y6">
+        <v>0.349</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>3.9</v>
+      </c>
+      <c r="AB6">
+        <v>0.8794</v>
       </c>
       <c r="AC6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD6">
+        <v>0.1895</v>
+      </c>
+      <c r="AE6">
+        <v>0.2056</v>
+      </c>
+      <c r="AF6">
+        <v>9</v>
+      </c>
+      <c r="AG6">
+        <v>0.2371</v>
+      </c>
+      <c r="AH6">
+        <v>0.2154</v>
+      </c>
+      <c r="AI6">
+        <v>1.0903</v>
+      </c>
+      <c r="AJ6" t="b">
+        <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1218,70 +1359,91 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7">
-        <v>6.5</v>
-      </c>
-      <c r="D7">
-        <v>-103</v>
-      </c>
-      <c r="E7">
-        <v>-112</v>
+        <v>60</v>
       </c>
       <c r="F7">
-        <v>5.88</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
+        <v>3.84</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
       </c>
-      <c r="I7">
-        <v>-0.62</v>
-      </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K7">
-        <v>6.48</v>
+        <v>3.68</v>
       </c>
       <c r="L7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N7">
-        <v>824162</v>
+        <v>823594</v>
       </c>
       <c r="O7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7">
+        <v>4.5</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0.1746</v>
+      </c>
+      <c r="U7">
+        <v>0.1764</v>
+      </c>
+      <c r="V7">
+        <v>5</v>
+      </c>
+      <c r="W7">
+        <v>83</v>
+      </c>
+      <c r="X7">
+        <v>0.1807</v>
+      </c>
+      <c r="Y7">
+        <v>0.293</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>4.3</v>
+      </c>
+      <c r="AB7">
+        <v>1.059</v>
+      </c>
+      <c r="AC7" t="s">
         <v>49</v>
       </c>
-      <c r="P7">
-        <v>5.5</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>6</v>
-      </c>
-      <c r="AA7">
-        <v>4.04</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>47</v>
+      <c r="AD7">
+        <v>0.2282</v>
+      </c>
+      <c r="AE7">
+        <v>0.2237</v>
+      </c>
+      <c r="AF7">
+        <v>9</v>
+      </c>
+      <c r="AG7">
+        <v>0.2241</v>
+      </c>
+      <c r="AH7">
+        <v>0.2154</v>
       </c>
       <c r="AI7">
-        <v>0.9835</v>
+        <v>1.0148</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
@@ -1292,17 +1454,8 @@
       <c r="AL7" t="s">
         <v>50</v>
       </c>
-      <c r="AN7">
-        <v>-3.48</v>
-      </c>
-      <c r="AO7">
-        <v>3.48</v>
-      </c>
-      <c r="AP7">
-        <v>-2.88</v>
-      </c>
-      <c r="AQ7">
-        <v>2.88</v>
+      <c r="AM7">
+        <v>0.16</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
@@ -1310,67 +1463,88 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8">
-        <v>4.5</v>
-      </c>
-      <c r="D8">
-        <v>-148</v>
-      </c>
-      <c r="E8">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="F8">
+        <v>3.34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8">
         <v>3.18</v>
       </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8">
-        <v>-1.32</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
         <v>46</v>
-      </c>
-      <c r="K8">
-        <v>3.78</v>
-      </c>
-      <c r="L8" t="s">
-        <v>47</v>
       </c>
       <c r="M8" t="s">
         <v>61</v>
       </c>
       <c r="N8">
-        <v>824405</v>
+        <v>823594</v>
       </c>
       <c r="O8" t="s">
+        <v>48</v>
+      </c>
+      <c r="P8">
+        <v>5.6</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0.1765</v>
+      </c>
+      <c r="U8">
+        <v>0.1681</v>
+      </c>
+      <c r="V8">
+        <v>5</v>
+      </c>
+      <c r="W8">
+        <v>111</v>
+      </c>
+      <c r="X8">
+        <v>0.1532</v>
+      </c>
+      <c r="Y8">
+        <v>0.357</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>3.89</v>
+      </c>
+      <c r="AB8">
+        <v>0.9822</v>
+      </c>
+      <c r="AC8" t="s">
         <v>49</v>
       </c>
-      <c r="P8">
-        <v>6</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>6</v>
-      </c>
-      <c r="AA8">
-        <v>3.96</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>47</v>
+      <c r="AD8">
+        <v>0.2116</v>
+      </c>
+      <c r="AE8">
+        <v>0.2073</v>
+      </c>
+      <c r="AF8">
+        <v>9</v>
+      </c>
+      <c r="AG8">
+        <v>0.2332</v>
+      </c>
+      <c r="AH8">
+        <v>0.2154</v>
       </c>
       <c r="AI8">
         <v>0.88</v>
@@ -1384,17 +1558,8 @@
       <c r="AL8" t="s">
         <v>50</v>
       </c>
-      <c r="AN8">
-        <v>2.22</v>
-      </c>
-      <c r="AO8">
-        <v>2.22</v>
-      </c>
-      <c r="AP8">
-        <v>2.82</v>
-      </c>
-      <c r="AQ8">
-        <v>2.82</v>
+      <c r="AM8">
+        <v>0.16</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
@@ -1402,52 +1567,112 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D9">
-        <v>101</v>
+        <v>-108</v>
       </c>
       <c r="E9">
-        <v>-122</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
+        <v>-112</v>
+      </c>
+      <c r="F9">
+        <v>8.27</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>8.27</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M9" t="s">
-        <v>61</v>
-      </c>
-      <c r="N9" t="s">
-        <v>47</v>
+        <v>64</v>
+      </c>
+      <c r="N9">
+        <v>824485</v>
       </c>
       <c r="O9" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="P9">
+        <v>5.8</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
       </c>
       <c r="S9">
         <v>6</v>
       </c>
+      <c r="T9">
+        <v>0.2656</v>
+      </c>
+      <c r="U9">
+        <v>0.2479</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>107</v>
+      </c>
+      <c r="X9">
+        <v>0.215</v>
+      </c>
+      <c r="Y9">
+        <v>0.349</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>4.13</v>
+      </c>
+      <c r="AB9">
+        <v>1.3077</v>
+      </c>
       <c r="AC9" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD9">
+        <v>0.2817</v>
+      </c>
+      <c r="AE9">
+        <v>0.2715</v>
+      </c>
+      <c r="AF9">
+        <v>9</v>
+      </c>
+      <c r="AG9">
+        <v>0.2549</v>
+      </c>
+      <c r="AH9">
+        <v>0.2154</v>
+      </c>
+      <c r="AI9">
+        <v>1.0741</v>
+      </c>
+      <c r="AJ9" t="b">
+        <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
@@ -1455,49 +1680,112 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E10">
-        <v>-139</v>
+        <v>-136</v>
+      </c>
+      <c r="F10">
+        <v>4.95</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="K10">
+        <v>4.79</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M10" t="s">
         <v>64</v>
       </c>
-      <c r="N10" t="s">
-        <v>47</v>
+      <c r="N10">
+        <v>824485</v>
       </c>
       <c r="O10" t="s">
-        <v>47</v>
+        <v>66</v>
+      </c>
+      <c r="P10">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
       </c>
       <c r="S10">
         <v>6</v>
       </c>
+      <c r="T10">
+        <v>0.1784</v>
+      </c>
+      <c r="U10">
+        <v>0.1693</v>
+      </c>
+      <c r="V10">
+        <v>5</v>
+      </c>
+      <c r="W10">
+        <v>117</v>
+      </c>
+      <c r="X10">
+        <v>0.1538</v>
+      </c>
+      <c r="Y10">
+        <v>0.369</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>4.31</v>
+      </c>
+      <c r="AB10">
+        <v>1.017</v>
+      </c>
       <c r="AC10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD10">
+        <v>0.2191</v>
+      </c>
+      <c r="AE10">
+        <v>0.2334</v>
+      </c>
+      <c r="AF10">
+        <v>9</v>
+      </c>
+      <c r="AG10">
+        <v>0.2572</v>
+      </c>
+      <c r="AH10">
+        <v>0.2154</v>
+      </c>
+      <c r="AI10">
+        <v>1.0748</v>
+      </c>
+      <c r="AJ10" t="b">
+        <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="AM10">
+        <v>0.16</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
@@ -1505,70 +1793,91 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11">
-        <v>2.5</v>
-      </c>
-      <c r="D11">
-        <v>100</v>
-      </c>
-      <c r="E11">
-        <v>-115</v>
+        <v>67</v>
       </c>
       <c r="F11">
-        <v>1.73</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
+        <v>7.79</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11">
-        <v>-0.77</v>
+        <v>45</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K11">
-        <v>2.33</v>
+        <v>7.79</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N11">
-        <v>824890</v>
+        <v>824808</v>
       </c>
       <c r="O11" t="s">
+        <v>48</v>
+      </c>
+      <c r="P11">
+        <v>6.2</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0.278</v>
+      </c>
+      <c r="U11">
+        <v>0.2806</v>
+      </c>
+      <c r="V11">
+        <v>5</v>
+      </c>
+      <c r="W11">
+        <v>130</v>
+      </c>
+      <c r="X11">
+        <v>0.2846</v>
+      </c>
+      <c r="Y11">
+        <v>0.394</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>4.18</v>
+      </c>
+      <c r="AB11">
+        <v>1.1007</v>
+      </c>
+      <c r="AC11" t="s">
         <v>49</v>
       </c>
-      <c r="P11">
-        <v>4.7</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>6</v>
-      </c>
-      <c r="AA11">
-        <v>4.26</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>47</v>
+      <c r="AD11">
+        <v>0.2371</v>
+      </c>
+      <c r="AE11">
+        <v>0.2305</v>
+      </c>
+      <c r="AF11">
+        <v>9</v>
+      </c>
+      <c r="AG11">
+        <v>0.2555</v>
+      </c>
+      <c r="AH11">
+        <v>0.2154</v>
       </c>
       <c r="AI11">
-        <v>1.0031</v>
+        <v>0.9672</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
@@ -1579,17 +1888,8 @@
       <c r="AL11" t="s">
         <v>50</v>
       </c>
-      <c r="AN11">
-        <v>0.67</v>
-      </c>
-      <c r="AO11">
-        <v>0.67</v>
-      </c>
-      <c r="AP11">
-        <v>1.27</v>
-      </c>
-      <c r="AQ11">
-        <v>1.27</v>
+      <c r="AM11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
@@ -1597,49 +1897,43 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C12">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D12">
-        <v>-138</v>
+        <v>110</v>
       </c>
       <c r="E12">
-        <v>117</v>
+        <v>-131</v>
       </c>
       <c r="F12">
-        <v>4.16</v>
-      </c>
-      <c r="G12">
-        <v>8</v>
+        <v>6.38</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12">
-        <v>-0.34</v>
+        <v>45</v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K12">
-        <v>4.76</v>
+        <v>6.38</v>
       </c>
       <c r="L12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="M12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N12">
-        <v>824649</v>
+        <v>824808</v>
       </c>
       <c r="O12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P12">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1650,17 +1944,53 @@
       <c r="S12">
         <v>6</v>
       </c>
+      <c r="T12">
+        <v>0.2073</v>
+      </c>
+      <c r="U12">
+        <v>0.224</v>
+      </c>
+      <c r="V12">
+        <v>5</v>
+      </c>
+      <c r="W12">
+        <v>119</v>
+      </c>
+      <c r="X12">
+        <v>0.2521</v>
+      </c>
+      <c r="Y12">
+        <v>0.373</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
       <c r="AA12">
-        <v>4.52</v>
+        <v>4.25</v>
+      </c>
+      <c r="AB12">
+        <v>1.1331</v>
       </c>
       <c r="AC12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD12">
+        <v>0.2441</v>
+      </c>
+      <c r="AE12">
+        <v>0.2483</v>
+      </c>
+      <c r="AF12">
+        <v>9</v>
+      </c>
+      <c r="AG12">
+        <v>0.2267</v>
+      </c>
+      <c r="AH12">
+        <v>0.2154</v>
       </c>
       <c r="AI12">
-        <v>1.0872</v>
+        <v>0.9984</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
@@ -1671,17 +2001,8 @@
       <c r="AL12" t="s">
         <v>50</v>
       </c>
-      <c r="AN12">
-        <v>3.24</v>
-      </c>
-      <c r="AO12">
-        <v>3.24</v>
-      </c>
-      <c r="AP12">
-        <v>3.84</v>
-      </c>
-      <c r="AQ12">
-        <v>3.84</v>
+      <c r="AM12">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
@@ -1689,49 +2010,43 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D13">
-        <v>-146</v>
+        <v>-103</v>
       </c>
       <c r="E13">
-        <v>128</v>
+        <v>-112</v>
       </c>
       <c r="F13">
-        <v>4.19</v>
-      </c>
-      <c r="G13">
-        <v>7</v>
+        <v>6.18</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13">
-        <v>-0.31</v>
+        <v>45</v>
       </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K13">
-        <v>4.79</v>
+        <v>6.18</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="M13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N13">
-        <v>824649</v>
+        <v>824162</v>
       </c>
       <c r="O13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P13">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -1742,17 +2057,53 @@
       <c r="S13">
         <v>6</v>
       </c>
+      <c r="T13">
+        <v>0.2963</v>
+      </c>
+      <c r="U13">
+        <v>0.2884</v>
+      </c>
+      <c r="V13">
+        <v>5</v>
+      </c>
+      <c r="W13">
+        <v>106</v>
+      </c>
+      <c r="X13">
+        <v>0.2736</v>
+      </c>
+      <c r="Y13">
+        <v>0.346</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
       <c r="AA13">
-        <v>3.89</v>
+        <v>4.1</v>
+      </c>
+      <c r="AB13">
+        <v>0.9904</v>
       </c>
       <c r="AC13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD13">
+        <v>0.2134</v>
+      </c>
+      <c r="AE13">
+        <v>0.2068</v>
+      </c>
+      <c r="AF13">
+        <v>9</v>
+      </c>
+      <c r="AG13">
+        <v>0.2164</v>
+      </c>
+      <c r="AH13">
+        <v>0.2154</v>
       </c>
       <c r="AI13">
-        <v>0.9855</v>
+        <v>0.9786</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
@@ -1763,17 +2114,8 @@
       <c r="AL13" t="s">
         <v>50</v>
       </c>
-      <c r="AN13">
-        <v>2.21</v>
-      </c>
-      <c r="AO13">
-        <v>2.21</v>
-      </c>
-      <c r="AP13">
-        <v>2.81</v>
-      </c>
-      <c r="AQ13">
-        <v>2.81</v>
+      <c r="AM13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
@@ -1781,49 +2123,43 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C14">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D14">
-        <v>-136</v>
+        <v>123</v>
       </c>
       <c r="E14">
-        <v>120</v>
+        <v>-143</v>
       </c>
       <c r="F14">
-        <v>3.49</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
+        <v>4.52</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
       </c>
-      <c r="I14">
-        <v>-0.01</v>
-      </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K14">
-        <v>4.09</v>
+        <v>4.36</v>
       </c>
       <c r="L14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N14">
-        <v>824326</v>
+        <v>824162</v>
       </c>
       <c r="O14" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="P14">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -1834,17 +2170,53 @@
       <c r="S14">
         <v>6</v>
       </c>
+      <c r="T14">
+        <v>0.2099</v>
+      </c>
+      <c r="U14">
+        <v>0.2099</v>
+      </c>
+      <c r="V14">
+        <v>4</v>
+      </c>
+      <c r="W14">
+        <v>81</v>
+      </c>
+      <c r="X14">
+        <v>0.2099</v>
+      </c>
+      <c r="Y14">
+        <v>0.288</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
       <c r="AA14">
-        <v>4.37</v>
+        <v>4.19</v>
+      </c>
+      <c r="AB14">
+        <v>1.0267</v>
       </c>
       <c r="AC14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD14">
+        <v>0.2212</v>
+      </c>
+      <c r="AE14">
+        <v>0.2103</v>
+      </c>
+      <c r="AF14">
+        <v>9</v>
+      </c>
+      <c r="AG14">
+        <v>0.2197</v>
+      </c>
+      <c r="AH14">
+        <v>0.2154</v>
       </c>
       <c r="AI14">
-        <v>1.0465</v>
+        <v>0.9988</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
@@ -1855,17 +2227,8 @@
       <c r="AL14" t="s">
         <v>50</v>
       </c>
-      <c r="AN14">
-        <v>-2.09</v>
-      </c>
-      <c r="AO14">
-        <v>2.09</v>
-      </c>
-      <c r="AP14">
-        <v>-1.49</v>
-      </c>
-      <c r="AQ14">
-        <v>1.49</v>
+      <c r="AM14">
+        <v>0.16</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
@@ -1873,49 +2236,43 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15">
         <v>3.5</v>
       </c>
       <c r="D15">
-        <v>-142</v>
+        <v>101</v>
       </c>
       <c r="E15">
-        <v>115</v>
+        <v>-122</v>
       </c>
       <c r="F15">
-        <v>2.84</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
       </c>
-      <c r="I15">
-        <v>-0.66</v>
-      </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K15">
-        <v>3.44</v>
+        <v>2.65</v>
       </c>
       <c r="L15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N15">
-        <v>824326</v>
+        <v>824405</v>
       </c>
       <c r="O15" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="P15">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -1926,17 +2283,53 @@
       <c r="S15">
         <v>6</v>
       </c>
+      <c r="T15">
+        <v>0.1688</v>
+      </c>
+      <c r="U15">
+        <v>0.1688</v>
+      </c>
+      <c r="V15">
+        <v>4</v>
+      </c>
+      <c r="W15">
+        <v>77</v>
+      </c>
+      <c r="X15">
+        <v>0.1688</v>
+      </c>
+      <c r="Y15">
+        <v>0.278</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
       <c r="AA15">
-        <v>4.36</v>
+        <v>4.62</v>
+      </c>
+      <c r="AB15">
+        <v>0.9264</v>
       </c>
       <c r="AC15" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD15">
+        <v>0.1996</v>
+      </c>
+      <c r="AE15">
+        <v>0.1911</v>
+      </c>
+      <c r="AF15">
+        <v>9</v>
+      </c>
+      <c r="AG15">
+        <v>0.2297</v>
+      </c>
+      <c r="AH15">
+        <v>0.2154</v>
       </c>
       <c r="AI15">
-        <v>0.9769</v>
+        <v>0.88</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
@@ -1947,16 +2340,7 @@
       <c r="AL15" t="s">
         <v>50</v>
       </c>
-      <c r="AN15">
-        <v>-0.44</v>
-      </c>
-      <c r="AO15">
-        <v>0.44</v>
-      </c>
-      <c r="AP15">
-        <v>0.16</v>
-      </c>
-      <c r="AQ15">
+      <c r="AM15">
         <v>0.16</v>
       </c>
     </row>
@@ -1965,49 +2349,43 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>128</v>
+        <v>-148</v>
       </c>
       <c r="E16">
-        <v>-161</v>
+        <v>125</v>
       </c>
       <c r="F16">
-        <v>4.22</v>
-      </c>
-      <c r="G16">
-        <v>9</v>
+        <v>4.58</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16">
-        <v>-0.28</v>
+        <v>45</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K16">
-        <v>4.82</v>
+        <v>4.42</v>
       </c>
       <c r="L16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M16" t="s">
         <v>74</v>
       </c>
       <c r="N16">
-        <v>823269</v>
+        <v>824405</v>
       </c>
       <c r="O16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P16">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2018,17 +2396,53 @@
       <c r="S16">
         <v>6</v>
       </c>
+      <c r="T16">
+        <v>0.2509</v>
+      </c>
+      <c r="U16">
+        <v>0.242</v>
+      </c>
+      <c r="V16">
+        <v>5</v>
+      </c>
+      <c r="W16">
+        <v>119</v>
+      </c>
+      <c r="X16">
+        <v>0.2269</v>
+      </c>
+      <c r="Y16">
+        <v>0.373</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
       <c r="AA16">
-        <v>4.26</v>
+        <v>3.97</v>
+      </c>
+      <c r="AB16">
+        <v>0.8817</v>
       </c>
       <c r="AC16" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD16">
+        <v>0.19</v>
+      </c>
+      <c r="AE16">
+        <v>0.1801</v>
+      </c>
+      <c r="AF16">
+        <v>9</v>
+      </c>
+      <c r="AG16">
+        <v>0.1717</v>
+      </c>
+      <c r="AH16">
+        <v>0.2154</v>
       </c>
       <c r="AI16">
-        <v>1.0169</v>
+        <v>0.88</v>
       </c>
       <c r="AJ16" t="b">
         <v>1</v>
@@ -2039,17 +2453,8 @@
       <c r="AL16" t="s">
         <v>50</v>
       </c>
-      <c r="AN16">
-        <v>4.18</v>
-      </c>
-      <c r="AO16">
-        <v>4.18</v>
-      </c>
-      <c r="AP16">
-        <v>4.78</v>
-      </c>
-      <c r="AQ16">
-        <v>4.78</v>
+      <c r="AM16">
+        <v>0.16</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
@@ -2057,46 +2462,40 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D17">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>-152</v>
+        <v>-115</v>
       </c>
       <c r="F17">
-        <v>2.97</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
+        <v>2.46</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
       </c>
-      <c r="I17">
-        <v>-1.53</v>
-      </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="K17">
-        <v>3.57</v>
+        <v>2.3</v>
       </c>
       <c r="L17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N17">
-        <v>823269</v>
+        <v>824890</v>
       </c>
       <c r="O17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P17">
         <v>4.8</v>
@@ -2110,17 +2509,53 @@
       <c r="S17">
         <v>6</v>
       </c>
+      <c r="T17">
+        <v>0.115</v>
+      </c>
+      <c r="U17">
+        <v>0.104</v>
+      </c>
+      <c r="V17">
+        <v>5</v>
+      </c>
+      <c r="W17">
+        <v>127</v>
+      </c>
+      <c r="X17">
+        <v>0.0866</v>
+      </c>
+      <c r="Y17">
+        <v>0.388</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
       <c r="AA17">
-        <v>4.34</v>
+        <v>4.31</v>
+      </c>
+      <c r="AB17">
+        <v>1.061</v>
       </c>
       <c r="AC17" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD17">
+        <v>0.2286</v>
+      </c>
+      <c r="AE17">
+        <v>0.2267</v>
+      </c>
+      <c r="AF17">
+        <v>9</v>
+      </c>
+      <c r="AG17">
+        <v>0.2179</v>
+      </c>
+      <c r="AH17">
+        <v>0.2154</v>
       </c>
       <c r="AI17">
-        <v>0.8945</v>
+        <v>1.0035</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
@@ -2131,17 +2566,8 @@
       <c r="AL17" t="s">
         <v>50</v>
       </c>
-      <c r="AN17">
-        <v>-2.57</v>
-      </c>
-      <c r="AO17">
-        <v>2.57</v>
-      </c>
-      <c r="AP17">
-        <v>-1.97</v>
-      </c>
-      <c r="AQ17">
-        <v>1.97</v>
+      <c r="AM17">
+        <v>0.16</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
@@ -2149,70 +2575,91 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18">
-        <v>5.5</v>
-      </c>
-      <c r="D18">
-        <v>116</v>
-      </c>
-      <c r="E18">
-        <v>-138</v>
+        <v>79</v>
       </c>
       <c r="F18">
-        <v>5.05</v>
-      </c>
-      <c r="G18">
-        <v>7</v>
+        <v>3.14</v>
       </c>
       <c r="H18" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18">
-        <v>-0.45</v>
+        <v>45</v>
       </c>
       <c r="J18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K18">
-        <v>5.65</v>
+        <v>2.98</v>
       </c>
       <c r="L18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M18" t="s">
         <v>78</v>
       </c>
       <c r="N18">
-        <v>823920</v>
+        <v>824890</v>
       </c>
       <c r="O18" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18">
+        <v>5.1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0.1916</v>
+      </c>
+      <c r="U18">
+        <v>0.1882</v>
+      </c>
+      <c r="V18">
+        <v>5</v>
+      </c>
+      <c r="W18">
+        <v>94</v>
+      </c>
+      <c r="X18">
+        <v>0.1809</v>
+      </c>
+      <c r="Y18">
+        <v>0.32</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>4.06</v>
+      </c>
+      <c r="AB18">
+        <v>0.7931</v>
+      </c>
+      <c r="AC18" t="s">
         <v>49</v>
       </c>
-      <c r="P18">
-        <v>5.6</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>6</v>
-      </c>
-      <c r="AA18">
-        <v>4.09</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>47</v>
+      <c r="AD18">
+        <v>0.1709</v>
+      </c>
+      <c r="AE18">
+        <v>0.1811</v>
+      </c>
+      <c r="AF18">
+        <v>9</v>
+      </c>
+      <c r="AG18">
+        <v>0.2352</v>
+      </c>
+      <c r="AH18">
+        <v>0.2154</v>
       </c>
       <c r="AI18">
-        <v>1.0517</v>
+        <v>0.9738</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
@@ -2223,17 +2670,8 @@
       <c r="AL18" t="s">
         <v>50</v>
       </c>
-      <c r="AN18">
-        <v>1.35</v>
-      </c>
-      <c r="AO18">
-        <v>1.35</v>
-      </c>
-      <c r="AP18">
-        <v>1.95</v>
-      </c>
-      <c r="AQ18">
-        <v>1.95</v>
+      <c r="AM18">
+        <v>0.16</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
@@ -2241,49 +2679,43 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-103</v>
+        <v>-146</v>
       </c>
       <c r="E19">
-        <v>-105</v>
+        <v>128</v>
       </c>
       <c r="F19">
-        <v>5.1</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
+        <v>5.38</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
       </c>
-      <c r="I19">
-        <v>-1.4</v>
-      </c>
       <c r="J19" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="K19">
-        <v>5.7</v>
+        <v>5.22</v>
       </c>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N19">
-        <v>823920</v>
+        <v>824649</v>
       </c>
       <c r="O19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P19">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -2294,17 +2726,53 @@
       <c r="S19">
         <v>6</v>
       </c>
+      <c r="T19">
+        <v>0.2404</v>
+      </c>
+      <c r="U19">
+        <v>0.2634</v>
+      </c>
+      <c r="V19">
+        <v>5</v>
+      </c>
+      <c r="W19">
+        <v>85</v>
+      </c>
+      <c r="X19">
+        <v>0.3176</v>
+      </c>
+      <c r="Y19">
+        <v>0.298</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
       <c r="AA19">
-        <v>3.83</v>
+        <v>3.84</v>
+      </c>
+      <c r="AB19">
+        <v>0.9185</v>
       </c>
       <c r="AC19" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD19">
+        <v>0.1979</v>
+      </c>
+      <c r="AE19">
+        <v>0.2243</v>
+      </c>
+      <c r="AF19">
+        <v>9</v>
+      </c>
+      <c r="AG19">
+        <v>0.2163</v>
+      </c>
+      <c r="AH19">
+        <v>0.2154</v>
       </c>
       <c r="AI19">
-        <v>0.897</v>
+        <v>0.9687</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
@@ -2315,17 +2783,8 @@
       <c r="AL19" t="s">
         <v>50</v>
       </c>
-      <c r="AN19">
-        <v>-2.7</v>
-      </c>
-      <c r="AO19">
-        <v>2.7</v>
-      </c>
-      <c r="AP19">
-        <v>-2.1</v>
-      </c>
-      <c r="AQ19">
-        <v>2.1</v>
+      <c r="AM19">
+        <v>0.16</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
@@ -2333,49 +2792,43 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20">
         <v>4.5</v>
       </c>
       <c r="D20">
-        <v>-154</v>
+        <v>-138</v>
       </c>
       <c r="E20">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F20">
-        <v>4.98</v>
-      </c>
-      <c r="G20">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="H20" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20">
-        <v>0.48</v>
+        <v>45</v>
       </c>
       <c r="J20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K20">
-        <v>5.58</v>
+        <v>6.06</v>
       </c>
       <c r="L20" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="M20" t="s">
         <v>81</v>
       </c>
       <c r="N20">
-        <v>824000</v>
+        <v>824649</v>
       </c>
       <c r="O20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P20">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -2386,17 +2839,53 @@
       <c r="S20">
         <v>6</v>
       </c>
+      <c r="T20">
+        <v>0.1849</v>
+      </c>
+      <c r="U20">
+        <v>0.1814</v>
+      </c>
+      <c r="V20">
+        <v>5</v>
+      </c>
+      <c r="W20">
+        <v>114</v>
+      </c>
+      <c r="X20">
+        <v>0.1754</v>
+      </c>
+      <c r="Y20">
+        <v>0.363</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
       <c r="AA20">
-        <v>4.22</v>
+        <v>4.49</v>
+      </c>
+      <c r="AB20">
+        <v>1.3557</v>
       </c>
       <c r="AC20" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD20">
+        <v>0.2921</v>
+      </c>
+      <c r="AE20">
+        <v>0.2923</v>
+      </c>
+      <c r="AF20">
+        <v>9</v>
+      </c>
+      <c r="AG20">
+        <v>0.249</v>
+      </c>
+      <c r="AH20">
+        <v>0.2154</v>
       </c>
       <c r="AI20">
-        <v>1.0304</v>
+        <v>1.0932</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
@@ -2407,17 +2896,8 @@
       <c r="AL20" t="s">
         <v>50</v>
       </c>
-      <c r="AN20">
-        <v>0.42</v>
-      </c>
-      <c r="AO20">
-        <v>0.42</v>
-      </c>
-      <c r="AP20">
-        <v>1.02</v>
-      </c>
-      <c r="AQ20">
-        <v>1.02</v>
+      <c r="AM20">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
@@ -2425,49 +2905,43 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D21">
-        <v>-120</v>
+        <v>-136</v>
       </c>
       <c r="E21">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F21">
-        <v>4.17</v>
-      </c>
-      <c r="G21">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21">
-        <v>-0.33</v>
+        <v>45</v>
       </c>
       <c r="J21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K21">
-        <v>4.77</v>
+        <v>4.09</v>
       </c>
       <c r="L21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N21">
-        <v>824972</v>
+        <v>824326</v>
       </c>
       <c r="O21" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="P21">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -2478,17 +2952,53 @@
       <c r="S21">
         <v>6</v>
       </c>
+      <c r="T21">
+        <v>0.1974</v>
+      </c>
+      <c r="U21">
+        <v>0.1897</v>
+      </c>
+      <c r="V21">
+        <v>5</v>
+      </c>
+      <c r="W21">
+        <v>103</v>
+      </c>
+      <c r="X21">
+        <v>0.1748</v>
+      </c>
+      <c r="Y21">
+        <v>0.34</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
       <c r="AA21">
-        <v>4.44</v>
+        <v>4.41</v>
+      </c>
+      <c r="AB21">
+        <v>1.0964</v>
       </c>
       <c r="AC21" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD21">
+        <v>0.2362</v>
+      </c>
+      <c r="AE21">
+        <v>0.2271</v>
+      </c>
+      <c r="AF21">
+        <v>9</v>
+      </c>
+      <c r="AG21">
+        <v>0.2165</v>
+      </c>
+      <c r="AH21">
+        <v>0.2154</v>
       </c>
       <c r="AI21">
-        <v>0.9938</v>
+        <v>1.0345</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
@@ -2499,17 +3009,8 @@
       <c r="AL21" t="s">
         <v>50</v>
       </c>
-      <c r="AN21">
-        <v>1.23</v>
-      </c>
-      <c r="AO21">
-        <v>1.23</v>
-      </c>
-      <c r="AP21">
-        <v>1.83</v>
-      </c>
-      <c r="AQ21">
-        <v>1.83</v>
+      <c r="AM21">
+        <v>0.16</v>
       </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
@@ -2517,49 +3018,43 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22">
+        <v>3.5</v>
+      </c>
+      <c r="D22">
+        <v>-142</v>
+      </c>
+      <c r="E22">
+        <v>115</v>
+      </c>
+      <c r="F22">
+        <v>2.92</v>
+      </c>
+      <c r="H22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22">
+        <v>2.76</v>
+      </c>
+      <c r="L22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M22" t="s">
         <v>84</v>
       </c>
-      <c r="C22">
-        <v>4.5</v>
-      </c>
-      <c r="D22">
-        <v>-105</v>
-      </c>
-      <c r="E22">
-        <v>108</v>
-      </c>
-      <c r="F22">
-        <v>5.07</v>
-      </c>
-      <c r="G22">
-        <v>9</v>
-      </c>
-      <c r="H22" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22">
-        <v>0.57</v>
-      </c>
-      <c r="J22" t="s">
-        <v>47</v>
-      </c>
-      <c r="K22">
-        <v>5.67</v>
-      </c>
-      <c r="L22" t="s">
-        <v>47</v>
-      </c>
-      <c r="M22" t="s">
-        <v>83</v>
-      </c>
       <c r="N22">
-        <v>824972</v>
+        <v>824326</v>
       </c>
       <c r="O22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P22">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -2570,17 +3065,53 @@
       <c r="S22">
         <v>6</v>
       </c>
+      <c r="T22">
+        <v>0.1648</v>
+      </c>
+      <c r="U22">
+        <v>0.1527</v>
+      </c>
+      <c r="V22">
+        <v>5</v>
+      </c>
+      <c r="W22">
+        <v>114</v>
+      </c>
+      <c r="X22">
+        <v>0.1316</v>
+      </c>
+      <c r="Y22">
+        <v>0.363</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
       <c r="AA22">
-        <v>4.48</v>
+        <v>4.37</v>
+      </c>
+      <c r="AB22">
+        <v>0.8958</v>
       </c>
       <c r="AC22" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD22">
+        <v>0.193</v>
+      </c>
+      <c r="AE22">
+        <v>0.2295</v>
+      </c>
+      <c r="AF22">
+        <v>9</v>
+      </c>
+      <c r="AG22">
+        <v>0.2095</v>
+      </c>
+      <c r="AH22">
+        <v>0.2154</v>
       </c>
       <c r="AI22">
-        <v>0.9996</v>
+        <v>0.9589</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
@@ -2591,17 +3122,8 @@
       <c r="AL22" t="s">
         <v>50</v>
       </c>
-      <c r="AN22">
-        <v>3.33</v>
-      </c>
-      <c r="AO22">
-        <v>3.33</v>
-      </c>
-      <c r="AP22">
-        <v>3.93</v>
-      </c>
-      <c r="AQ22">
-        <v>3.93</v>
+      <c r="AM22">
+        <v>0.16</v>
       </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.25">
@@ -2609,34 +3131,43 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="C23">
+        <v>4.5</v>
+      </c>
+      <c r="D23">
+        <v>128</v>
+      </c>
+      <c r="E23">
+        <v>-161</v>
       </c>
       <c r="F23">
-        <v>4.31</v>
+        <v>5.47</v>
       </c>
       <c r="H23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K23">
-        <v>4.91</v>
+        <v>5.31</v>
       </c>
       <c r="L23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N23">
-        <v>822781</v>
+        <v>823269</v>
       </c>
       <c r="O23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P23">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -2645,19 +3176,55 @@
         <v>0</v>
       </c>
       <c r="S23">
+        <v>6</v>
+      </c>
+      <c r="T23">
+        <v>0.2295</v>
+      </c>
+      <c r="U23">
+        <v>0.2348</v>
+      </c>
+      <c r="V23">
+        <v>5</v>
+      </c>
+      <c r="W23">
+        <v>119</v>
+      </c>
+      <c r="X23">
+        <v>0.2437</v>
+      </c>
+      <c r="Y23">
+        <v>0.373</v>
+      </c>
+      <c r="Z23" t="b">
         <v>0</v>
       </c>
       <c r="AA23">
         <v>4.24</v>
       </c>
+      <c r="AB23">
+        <v>0.9964</v>
+      </c>
       <c r="AC23" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD23">
+        <v>0.2147</v>
+      </c>
+      <c r="AE23">
+        <v>0.2128</v>
+      </c>
+      <c r="AF23">
+        <v>9</v>
+      </c>
+      <c r="AG23">
+        <v>0.2198</v>
+      </c>
+      <c r="AH23">
+        <v>0.2154</v>
       </c>
       <c r="AI23">
-        <v>0.9155</v>
+        <v>1.0093</v>
       </c>
       <c r="AJ23" t="b">
         <v>1</v>
@@ -2667,6 +3234,9 @@
       </c>
       <c r="AL23" t="s">
         <v>50</v>
+      </c>
+      <c r="AM23">
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
@@ -2674,55 +3244,100 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24">
+        <v>4.5</v>
+      </c>
+      <c r="D24">
+        <v>133</v>
+      </c>
+      <c r="E24">
+        <v>-152</v>
+      </c>
+      <c r="F24">
+        <v>4.22</v>
+      </c>
+      <c r="H24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" t="s">
+        <v>45</v>
+      </c>
+      <c r="K24">
+        <v>4.06</v>
+      </c>
+      <c r="L24" t="s">
+        <v>46</v>
+      </c>
+      <c r="M24" t="s">
         <v>87</v>
       </c>
-      <c r="F24">
-        <v>5.42</v>
-      </c>
-      <c r="H24" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" t="s">
-        <v>47</v>
-      </c>
-      <c r="K24">
-        <v>6.02</v>
-      </c>
-      <c r="L24" t="s">
-        <v>47</v>
-      </c>
-      <c r="M24" t="s">
-        <v>88</v>
-      </c>
       <c r="N24">
-        <v>823109</v>
+        <v>823269</v>
       </c>
       <c r="O24" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24">
+        <v>4.7</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>6</v>
+      </c>
+      <c r="T24">
+        <v>0.2008</v>
+      </c>
+      <c r="U24">
+        <v>0.1851</v>
+      </c>
+      <c r="V24">
+        <v>5</v>
+      </c>
+      <c r="W24">
+        <v>98</v>
+      </c>
+      <c r="X24">
+        <v>0.1531</v>
+      </c>
+      <c r="Y24">
+        <v>0.329</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>4.37</v>
+      </c>
+      <c r="AB24">
+        <v>1.0886</v>
+      </c>
+      <c r="AC24" t="s">
         <v>49</v>
       </c>
-      <c r="P24">
-        <v>5.2</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
-      <c r="R24" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>4.33</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>47</v>
+      <c r="AD24">
+        <v>0.2345</v>
+      </c>
+      <c r="AE24">
+        <v>0.2265</v>
+      </c>
+      <c r="AF24">
+        <v>9</v>
+      </c>
+      <c r="AG24">
+        <v>0.2019</v>
+      </c>
+      <c r="AH24">
+        <v>0.2154</v>
       </c>
       <c r="AI24">
-        <v>1.0467</v>
+        <v>0.9798</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
@@ -2732,6 +3347,9 @@
       </c>
       <c r="AL24" t="s">
         <v>50</v>
+      </c>
+      <c r="AM24">
+        <v>0.16</v>
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
@@ -2741,53 +3359,98 @@
       <c r="B25" t="s">
         <v>89</v>
       </c>
+      <c r="C25">
+        <v>5.5</v>
+      </c>
+      <c r="D25">
+        <v>116</v>
+      </c>
+      <c r="E25">
+        <v>-138</v>
+      </c>
       <c r="F25">
-        <v>5.15</v>
+        <v>7.85</v>
       </c>
       <c r="H25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K25">
-        <v>5.75</v>
+        <v>7.85</v>
       </c>
       <c r="L25" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N25">
-        <v>823109</v>
+        <v>823920</v>
       </c>
       <c r="O25" t="s">
+        <v>48</v>
+      </c>
+      <c r="P25">
+        <v>5.6</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>6</v>
+      </c>
+      <c r="T25">
+        <v>0.2851</v>
+      </c>
+      <c r="U25">
+        <v>0.3269</v>
+      </c>
+      <c r="V25">
+        <v>5</v>
+      </c>
+      <c r="W25">
+        <v>109</v>
+      </c>
+      <c r="X25">
+        <v>0.4037</v>
+      </c>
+      <c r="Y25">
+        <v>0.353</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>4.07</v>
+      </c>
+      <c r="AB25">
+        <v>1.0066</v>
+      </c>
+      <c r="AC25" t="s">
         <v>49</v>
       </c>
-      <c r="P25">
-        <v>6</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>0</v>
-      </c>
-      <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>3.93</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>47</v>
+      <c r="AD25">
+        <v>0.2169</v>
+      </c>
+      <c r="AE25">
+        <v>0.227</v>
+      </c>
+      <c r="AF25">
+        <v>9</v>
+      </c>
+      <c r="AG25">
+        <v>0.1984</v>
+      </c>
+      <c r="AH25">
+        <v>0.2154</v>
       </c>
       <c r="AI25">
-        <v>0.9398</v>
+        <v>1.0414</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
@@ -2797,6 +3460,9 @@
       </c>
       <c r="AL25" t="s">
         <v>50</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.25">
@@ -2804,55 +3470,100 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26">
+        <v>6.5</v>
+      </c>
+      <c r="D26">
+        <v>-103</v>
+      </c>
+      <c r="E26">
+        <v>-105</v>
+      </c>
+      <c r="F26">
+        <v>4.94</v>
+      </c>
+      <c r="H26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J26" t="s">
+        <v>45</v>
+      </c>
+      <c r="K26">
+        <v>4.78</v>
+      </c>
+      <c r="L26" t="s">
+        <v>46</v>
+      </c>
+      <c r="M26" t="s">
         <v>90</v>
       </c>
-      <c r="F26">
-        <v>0.31</v>
-      </c>
-      <c r="H26" t="s">
-        <v>47</v>
-      </c>
-      <c r="J26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K26">
-        <v>0.91</v>
-      </c>
-      <c r="L26" t="s">
-        <v>47</v>
-      </c>
-      <c r="M26" t="s">
-        <v>91</v>
-      </c>
       <c r="N26">
-        <v>822944</v>
+        <v>823920</v>
       </c>
       <c r="O26" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="P26">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="Q26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26">
+        <v>6</v>
+      </c>
+      <c r="T26">
+        <v>0.2383</v>
+      </c>
+      <c r="U26">
+        <v>0.2229</v>
+      </c>
+      <c r="V26">
+        <v>5</v>
+      </c>
+      <c r="W26">
+        <v>135</v>
+      </c>
+      <c r="X26">
+        <v>0.2</v>
+      </c>
+      <c r="Y26">
+        <v>0.403</v>
+      </c>
+      <c r="Z26" t="b">
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>4.38</v>
+        <v>3.83</v>
+      </c>
+      <c r="AB26">
+        <v>0.9374</v>
       </c>
       <c r="AC26" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="AD26">
+        <v>0.2019</v>
+      </c>
+      <c r="AE26">
+        <v>0.195</v>
+      </c>
+      <c r="AF26">
+        <v>9</v>
+      </c>
+      <c r="AG26">
+        <v>0.2185</v>
+      </c>
+      <c r="AH26">
+        <v>0.2154</v>
       </c>
       <c r="AI26">
-        <v>0.88</v>
+        <v>0.9007</v>
       </c>
       <c r="AJ26" t="b">
         <v>1</v>
@@ -2862,6 +3573,9 @@
       </c>
       <c r="AL26" t="s">
         <v>50</v>
+      </c>
+      <c r="AM26">
+        <v>0.16</v>
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
@@ -2869,55 +3583,100 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27">
+        <v>4.5</v>
+      </c>
+      <c r="D27">
+        <v>-154</v>
+      </c>
+      <c r="E27">
+        <v>128</v>
+      </c>
+      <c r="F27">
+        <v>5.32</v>
+      </c>
+      <c r="H27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J27" t="s">
+        <v>45</v>
+      </c>
+      <c r="K27">
+        <v>5.16</v>
+      </c>
+      <c r="L27" t="s">
+        <v>46</v>
+      </c>
+      <c r="M27" t="s">
         <v>93</v>
       </c>
-      <c r="F27">
+      <c r="N27">
+        <v>824000</v>
+      </c>
+      <c r="O27" t="s">
+        <v>48</v>
+      </c>
+      <c r="P27">
+        <v>5.2</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27">
         <v>6</v>
       </c>
-      <c r="H27" t="s">
-        <v>47</v>
-      </c>
-      <c r="J27" t="s">
-        <v>47</v>
-      </c>
-      <c r="K27">
-        <v>6.6</v>
-      </c>
-      <c r="L27" t="s">
-        <v>47</v>
-      </c>
-      <c r="M27" t="s">
-        <v>91</v>
-      </c>
-      <c r="N27">
-        <v>822944</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="T27">
+        <v>0.2133</v>
+      </c>
+      <c r="U27">
+        <v>0.2101</v>
+      </c>
+      <c r="V27">
+        <v>5</v>
+      </c>
+      <c r="W27">
+        <v>103</v>
+      </c>
+      <c r="X27">
+        <v>0.2039</v>
+      </c>
+      <c r="Y27">
+        <v>0.34</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>4.27</v>
+      </c>
+      <c r="AB27">
+        <v>1.0688</v>
+      </c>
+      <c r="AC27" t="s">
         <v>49</v>
       </c>
-      <c r="P27">
-        <v>5.6</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>0</v>
-      </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>3.93</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>47</v>
+      <c r="AD27">
+        <v>0.2303</v>
+      </c>
+      <c r="AE27">
+        <v>0.2556</v>
+      </c>
+      <c r="AF27">
+        <v>9</v>
+      </c>
+      <c r="AG27">
+        <v>0.2626</v>
+      </c>
+      <c r="AH27">
+        <v>0.2154</v>
       </c>
       <c r="AI27">
-        <v>1.0667</v>
+        <v>1.0448</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
@@ -2927,6 +3686,9 @@
       </c>
       <c r="AL27" t="s">
         <v>50</v>
+      </c>
+      <c r="AM27">
+        <v>0.16</v>
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
@@ -2937,52 +3699,88 @@
         <v>94</v>
       </c>
       <c r="F28">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="H28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K28">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="L28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N28">
-        <v>823594</v>
+        <v>824000</v>
       </c>
       <c r="O28" t="s">
+        <v>57</v>
+      </c>
+      <c r="P28">
+        <v>1.9</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0.207</v>
+      </c>
+      <c r="U28">
+        <v>0.2</v>
+      </c>
+      <c r="V28">
+        <v>3</v>
+      </c>
+      <c r="W28">
+        <v>27</v>
+      </c>
+      <c r="X28">
+        <v>0.1481</v>
+      </c>
+      <c r="Y28">
+        <v>0.119</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>4.17</v>
+      </c>
+      <c r="AB28">
+        <v>0.9207</v>
+      </c>
+      <c r="AC28" t="s">
         <v>49</v>
       </c>
-      <c r="P28">
-        <v>4.6</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>0</v>
-      </c>
-      <c r="R28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>4.29</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>47</v>
+      <c r="AD28">
+        <v>0.1983</v>
+      </c>
+      <c r="AE28">
+        <v>0.2021</v>
+      </c>
+      <c r="AF28">
+        <v>9</v>
+      </c>
+      <c r="AG28">
+        <v>0.2163</v>
+      </c>
+      <c r="AH28">
+        <v>0.2154</v>
       </c>
       <c r="AI28">
-        <v>1.0186</v>
+        <v>1.014</v>
       </c>
       <c r="AJ28" t="b">
         <v>1</v>
@@ -2992,6 +3790,9 @@
       </c>
       <c r="AL28" t="s">
         <v>50</v>
+      </c>
+      <c r="AM28">
+        <v>0.16</v>
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
@@ -2999,55 +3800,100 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29">
+        <v>4.5</v>
+      </c>
+      <c r="D29">
+        <v>-120</v>
+      </c>
+      <c r="E29">
+        <v>110</v>
+      </c>
+      <c r="F29">
+        <v>4.3</v>
+      </c>
+      <c r="H29" t="s">
+        <v>45</v>
+      </c>
+      <c r="J29" t="s">
+        <v>45</v>
+      </c>
+      <c r="K29">
+        <v>4.14</v>
+      </c>
+      <c r="L29" t="s">
+        <v>46</v>
+      </c>
+      <c r="M29" t="s">
         <v>96</v>
       </c>
-      <c r="F29">
-        <v>3.1</v>
-      </c>
-      <c r="H29" t="s">
-        <v>47</v>
-      </c>
-      <c r="J29" t="s">
-        <v>47</v>
-      </c>
-      <c r="K29">
-        <v>3.7</v>
-      </c>
-      <c r="L29" t="s">
-        <v>47</v>
-      </c>
-      <c r="M29" t="s">
-        <v>95</v>
-      </c>
       <c r="N29">
-        <v>823594</v>
+        <v>824972</v>
       </c>
       <c r="O29" t="s">
+        <v>48</v>
+      </c>
+      <c r="P29">
+        <v>5.5</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>6</v>
+      </c>
+      <c r="T29">
+        <v>0.1846</v>
+      </c>
+      <c r="U29">
+        <v>0.1966</v>
+      </c>
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29">
+        <v>115</v>
+      </c>
+      <c r="X29">
+        <v>0.2174</v>
+      </c>
+      <c r="Y29">
+        <v>0.365</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>4.38</v>
+      </c>
+      <c r="AB29">
+        <v>0.8591</v>
+      </c>
+      <c r="AC29" t="s">
         <v>49</v>
       </c>
-      <c r="P29">
-        <v>5.7</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>0</v>
-      </c>
-      <c r="R29" t="b">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>3.9</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>47</v>
+      <c r="AD29">
+        <v>0.1851</v>
+      </c>
+      <c r="AE29">
+        <v>0.2004</v>
+      </c>
+      <c r="AF29">
+        <v>9</v>
+      </c>
+      <c r="AG29">
+        <v>0.2494</v>
+      </c>
+      <c r="AH29">
+        <v>0.2154</v>
       </c>
       <c r="AI29">
-        <v>0.88</v>
+        <v>1.0106</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
@@ -3057,6 +3903,9 @@
       </c>
       <c r="AL29" t="s">
         <v>50</v>
+      </c>
+      <c r="AM29">
+        <v>0.16</v>
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
@@ -3066,53 +3915,98 @@
       <c r="B30" t="s">
         <v>97</v>
       </c>
+      <c r="C30">
+        <v>4.5</v>
+      </c>
+      <c r="D30">
+        <v>-105</v>
+      </c>
+      <c r="E30">
+        <v>108</v>
+      </c>
       <c r="F30">
-        <v>6.95</v>
+        <v>4.69</v>
       </c>
       <c r="H30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K30">
-        <v>7.55</v>
+        <v>4.53</v>
       </c>
       <c r="L30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M30" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="N30">
-        <v>824808</v>
+        <v>824972</v>
       </c>
       <c r="O30" t="s">
+        <v>48</v>
+      </c>
+      <c r="P30">
+        <v>4.6</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>6</v>
+      </c>
+      <c r="T30">
+        <v>0.2636</v>
+      </c>
+      <c r="U30">
+        <v>0.2621</v>
+      </c>
+      <c r="V30">
+        <v>5</v>
+      </c>
+      <c r="W30">
+        <v>108</v>
+      </c>
+      <c r="X30">
+        <v>0.2593</v>
+      </c>
+      <c r="Y30">
+        <v>0.351</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>4.55</v>
+      </c>
+      <c r="AB30">
+        <v>0.8366</v>
+      </c>
+      <c r="AC30" t="s">
         <v>49</v>
       </c>
-      <c r="P30">
-        <v>6.3</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>4.17</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>47</v>
+      <c r="AD30">
+        <v>0.1802</v>
+      </c>
+      <c r="AE30">
+        <v>0.2102</v>
+      </c>
+      <c r="AF30">
+        <v>9</v>
+      </c>
+      <c r="AG30">
+        <v>0.2261</v>
+      </c>
+      <c r="AH30">
+        <v>0.2154</v>
       </c>
       <c r="AI30">
-        <v>0.9459</v>
+        <v>0.9928</v>
       </c>
       <c r="AJ30" t="b">
         <v>1</v>
@@ -3122,6 +4016,9 @@
       </c>
       <c r="AL30" t="s">
         <v>50</v>
+      </c>
+      <c r="AM30">
+        <v>0.16</v>
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
@@ -3131,62 +4028,47 @@
       <c r="B31" t="s">
         <v>98</v>
       </c>
-      <c r="F31">
-        <v>3.16</v>
+      <c r="C31">
+        <v>7.5</v>
+      </c>
+      <c r="D31">
+        <v>124</v>
+      </c>
+      <c r="E31">
+        <v>-156</v>
       </c>
       <c r="H31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J31" t="s">
-        <v>47</v>
-      </c>
-      <c r="K31">
-        <v>3.76</v>
+        <v>45</v>
       </c>
       <c r="L31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M31" t="s">
-        <v>64</v>
-      </c>
-      <c r="N31">
-        <v>824890</v>
+        <v>68</v>
+      </c>
+      <c r="N31" t="s">
+        <v>45</v>
       </c>
       <c r="O31" t="s">
-        <v>49</v>
-      </c>
-      <c r="P31">
-        <v>4.5</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>4.27</v>
+        <v>6</v>
       </c>
       <c r="AC31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF31" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI31">
-        <v>0.9812</v>
-      </c>
-      <c r="AJ31" t="b">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="AK31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AL31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
@@ -3196,62 +4078,47 @@
       <c r="B32" t="s">
         <v>99</v>
       </c>
-      <c r="F32">
-        <v>0.85</v>
+      <c r="C32">
+        <v>4.5</v>
+      </c>
+      <c r="D32">
+        <v>115</v>
+      </c>
+      <c r="E32">
+        <v>-139</v>
       </c>
       <c r="H32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J32" t="s">
-        <v>47</v>
-      </c>
-      <c r="K32">
-        <v>1.45</v>
+        <v>45</v>
       </c>
       <c r="L32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N32">
-        <v>824000</v>
+        <v>78</v>
+      </c>
+      <c r="N32" t="s">
+        <v>45</v>
       </c>
       <c r="O32" t="s">
-        <v>92</v>
-      </c>
-      <c r="P32">
-        <v>1.8</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>1</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>4.17</v>
+        <v>6</v>
       </c>
       <c r="AC32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF32" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI32">
-        <v>0.9903</v>
-      </c>
-      <c r="AJ32" t="b">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="AK32" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="AL32" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
@@ -3259,49 +4126,114 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>3.16</v>
+      </c>
+      <c r="H33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33" t="s">
+        <v>45</v>
+      </c>
+      <c r="K33">
+        <v>3.76</v>
+      </c>
+      <c r="L33" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" t="s">
+        <v>78</v>
+      </c>
+      <c r="N33">
+        <v>824890</v>
+      </c>
+      <c r="O33" t="s">
+        <v>48</v>
+      </c>
+      <c r="P33">
+        <v>4.5</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>4.27</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI33">
+        <v>0.9812</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="s">
         <v>101</v>
       </c>
-      <c r="C33">
+      <c r="C34">
         <v>1.5</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <v>-165</v>
       </c>
-      <c r="E33">
+      <c r="E34">
         <v>120</v>
       </c>
-      <c r="H33" t="s">
-        <v>47</v>
-      </c>
-      <c r="J33" t="s">
-        <v>47</v>
-      </c>
-      <c r="L33" t="s">
-        <v>47</v>
-      </c>
-      <c r="M33" t="s">
-        <v>95</v>
-      </c>
-      <c r="N33" t="s">
-        <v>47</v>
-      </c>
-      <c r="O33" t="s">
-        <v>47</v>
-      </c>
-      <c r="S33">
+      <c r="H34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" t="s">
+        <v>45</v>
+      </c>
+      <c r="L34" t="s">
+        <v>45</v>
+      </c>
+      <c r="M34" t="s">
+        <v>61</v>
+      </c>
+      <c r="N34" t="s">
+        <v>45</v>
+      </c>
+      <c r="O34" t="s">
+        <v>45</v>
+      </c>
+      <c r="S34">
         <v>1</v>
       </c>
-      <c r="AC33" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK33" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>47</v>
+      <c r="AC34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
